--- a/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
@@ -2733,7 +2733,7 @@
     <mergeCell ref="A2:F2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Reuniões!$A$5:$A$104</formula1>
     </dataValidation>
   </dataValidations>
@@ -4678,7 +4678,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="B5:B104" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="B5:B104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>
@@ -12564,10 +12564,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A5:A304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Reuniões!$A$5:$A$104</formula1>
     </dataValidation>
-    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>=Config!$A$9:$A$20</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
@@ -12576,7 +12576,7 @@
     <dataValidation sqref="F5:F304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list">
       <formula1>"A fazer,Fazendo,Feito"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D304 G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="date" operator="greaterThan">
+    <dataValidation sqref="D5:D304 G5:G304" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="date" operator="greaterThan">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
@@ -24,8 +24,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -49,6 +50,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="007A5AA8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="003B1F5E"/>
       <sz val="10"/>
@@ -57,11 +63,6 @@
       <name val="Arial"/>
       <color rgb="001F1235"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="007A5AA8"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -206,7 +207,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -239,43 +240,43 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -680,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -721,7 +722,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Em Config, preencha o nome da equipe e as pessoas. Deixe a data de referência em =HOJE().</t>
+          <t>Em Config, preencha o nome da equipe e as pessoas. Troque a data de referência por =HOJE() (no exemplo ela está congelada em 14/09/2026).</t>
         </is>
       </c>
     </row>
@@ -812,34 +813,58 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Google Sheets</t>
+          <t>Requisitos</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Excel 2016 ou mais novo, Microsoft 365 ou Google Sheets (só funções do Excel 2007+; nada de MÍNIMOSES, MÁXIMOSES ou UNIRTEXTO). No celular abre nos aplicativos; para preencher, use o computador.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Exemplos</t>
+          <t>Google Sheets</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Exemplos</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Prisma Comunicação é uma empresa fictícia. Nomes e valores são inventados. Apague-os antes de começar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -873,7 +898,7 @@
     <row r="1">
       <c r="A1" s="5" t="str">
         <f>Config!B4&amp;" · pendências em "&amp;TEXT(Config!B5,"dd/mm/yyyy")</f>
-        <v>Prisma Comunicação (exemplo fictício) · pendências em 17/09/2026</v>
+        <v>Prisma Comunicação (exemplo fictício) · pendências em 14/09/2026</v>
       </c>
     </row>
     <row r="2">
@@ -917,7 +942,7 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="16">
         <f>COUNTIFS(Pendências!$H$5:$H$304,"Atrasada")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="17">
@@ -1017,7 +1042,7 @@
       </c>
       <c r="H10" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,1)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,1),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,1),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11">
@@ -1026,15 +1051,15 @@
       </c>
       <c r="B11" s="22" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Fechar o manual da marca da Padaria</v>
+        <v>Confirmar a reunião de quarta com o Bistrô</v>
       </c>
       <c r="C11" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Carla</v>
+        <v>Ana</v>
       </c>
       <c r="D11" s="23">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>46280.0</v>
+        <v>46276.0</v>
       </c>
       <c r="E11" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
@@ -1042,7 +1067,7 @@
       </c>
       <c r="F11" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Alta</v>
+        <v>Média</v>
       </c>
       <c r="G11" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
@@ -1050,7 +1075,7 @@
       </c>
       <c r="H11" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,2)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,2),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="12">
@@ -1059,7 +1084,7 @@
       </c>
       <c r="B12" s="22" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Confirmar a reunião de quarta com o Bistrô</v>
+        <v>Levantar custo do freela de motion</v>
       </c>
       <c r="C12" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
@@ -1067,7 +1092,7 @@
       </c>
       <c r="D12" s="23">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>46276.0</v>
+        <v>46278.0</v>
       </c>
       <c r="E12" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
@@ -1075,7 +1100,7 @@
       </c>
       <c r="F12" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Média</v>
+        <v>Baixa</v>
       </c>
       <c r="G12" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
@@ -1083,7 +1108,7 @@
       </c>
       <c r="H12" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,3)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,3),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>-6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="13">
@@ -1092,31 +1117,31 @@
       </c>
       <c r="B13" s="22" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Enviar 3 referências de diagramação</v>
+        <v>Fechar o manual da marca da Padaria</v>
       </c>
       <c r="C13" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Bruno</v>
+        <v>Carla</v>
       </c>
       <c r="D13" s="23">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>46281.0</v>
+        <v>46280.0</v>
       </c>
       <c r="E13" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Atrasada</v>
+        <v>Esta semana</v>
       </c>
       <c r="F13" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Média</v>
+        <v>Alta</v>
       </c>
       <c r="G13" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>R-003</v>
+        <v>R-004</v>
       </c>
       <c r="H13" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,4)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,4),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1125,31 +1150,31 @@
       </c>
       <c r="B14" s="22" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$B$5:$B$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Levantar custo do freela de motion</v>
+        <v>Enviar 3 referências de diagramação</v>
       </c>
       <c r="C14" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$C$5:$C$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Ana</v>
+        <v>Bruno</v>
       </c>
       <c r="D14" s="23">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$D$5:$D$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>46278.0</v>
+        <v>46281.0</v>
       </c>
       <c r="E14" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$H$5:$H$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Atrasada</v>
+        <v>Esta semana</v>
       </c>
       <c r="F14" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$E$5:$E$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>Baixa</v>
+        <v>Média</v>
       </c>
       <c r="G14" s="21" t="str">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$A$5:$A$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>R-004</v>
+        <v>R-003</v>
       </c>
       <c r="H14" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,5)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,5),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>-4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1182,7 +1207,7 @@
       </c>
       <c r="H15" s="24">
         <f>IFERROR(IF(LARGE(Pendências!$J$5:$J$304,6)&gt;0,IF(INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,6),Pendências!$J$5:$J$304,0))="","",INDEX(Pendências!$I$5:$I$304,MATCH(LARGE(Pendências!$J$5:$J$304,6),Pendências!$J$5:$J$304,0))),""),"")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1558,11 +1583,11 @@
       </c>
       <c r="C29" s="21">
         <f>IF(Config!$A$10="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$10,Pendências!$H$5:$H$304,"Atrasada"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="21">
         <f>IF(Config!$A$10="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$10,Pendências!$H$5:$H$304,"Esta semana")+COUNTIFS(Pendências!$C$5:$C$304,Config!$A$10,Pendências!$H$5:$H$304,"Hoje"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="21">
         <f>IF(Config!$A$10="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$10,Pendências!$F$5:$F$304,"Feito"))</f>
@@ -1584,11 +1609,11 @@
       </c>
       <c r="C30" s="21">
         <f>IF(Config!$A$11="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$11,Pendências!$H$5:$H$304,"Atrasada"))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" s="21">
         <f>IF(Config!$A$11="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$11,Pendências!$H$5:$H$304,"Esta semana")+COUNTIFS(Pendências!$C$5:$C$304,Config!$A$11,Pendências!$H$5:$H$304,"Hoje"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="21">
         <f>IF(Config!$A$11="","",COUNTIFS(Pendências!$C$5:$C$304,Config!$A$11,Pendências!$F$5:$F$304,"Feito"))</f>
@@ -2000,11 +2025,11 @@
       </c>
       <c r="F11" s="21" t="str">
         <f>IFERROR(IF(INDEX(Pendências!$H$5:$H$304,MATCH(1,Pendências!$K$5:$K$304,0))="","",INDEX(Pendências!$H$5:$H$304,MATCH(1,Pendências!$K$5:$K$304,0))),"")</f>
-        <v>Atrasada</v>
+        <v>Esta semana</v>
       </c>
       <c r="H11" s="28" t="str">
         <f>""&amp;IF(B11="","",B11&amp;" (dono: "&amp;C11&amp;"; prazo: "&amp;IF(D11="","sem prazo",TEXT(D11,"dd/mm"))&amp;IF(F11="Sem prazo","","; "&amp;LOWER(F11))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | </v>
       </c>
     </row>
     <row r="12">
@@ -2033,7 +2058,7 @@
       </c>
       <c r="H12" s="28" t="str">
         <f>H11&amp;IF(B12="","",B12&amp;" (dono: "&amp;C12&amp;"; prazo: "&amp;IF(D12="","sem prazo",TEXT(D12,"dd/mm"))&amp;IF(F12="Sem prazo","","; "&amp;LOWER(F12))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | </v>
       </c>
     </row>
     <row r="13">
@@ -2062,7 +2087,7 @@
       </c>
       <c r="H13" s="28" t="str">
         <f>H12&amp;IF(B13="","",B13&amp;" (dono: "&amp;C13&amp;"; prazo: "&amp;IF(D13="","sem prazo",TEXT(D13,"dd/mm"))&amp;IF(F13="Sem prazo","","; "&amp;LOWER(F13))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | </v>
       </c>
     </row>
     <row r="14">
@@ -2091,7 +2116,7 @@
       </c>
       <c r="H14" s="28" t="str">
         <f>H13&amp;IF(B14="","",B14&amp;" (dono: "&amp;C14&amp;"; prazo: "&amp;IF(D14="","sem prazo",TEXT(D14,"dd/mm"))&amp;IF(F14="Sem prazo","","; "&amp;LOWER(F14))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | </v>
       </c>
     </row>
     <row r="15">
@@ -2120,7 +2145,7 @@
       </c>
       <c r="H15" s="28" t="str">
         <f>H14&amp;IF(B15="","",B15&amp;" (dono: "&amp;C15&amp;"; prazo: "&amp;IF(D15="","sem prazo",TEXT(D15,"dd/mm"))&amp;IF(F15="Sem prazo","","; "&amp;LOWER(F15))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="16">
@@ -2149,7 +2174,7 @@
       </c>
       <c r="H16" s="28" t="str">
         <f>H15&amp;IF(B16="","",B16&amp;" (dono: "&amp;C16&amp;"; prazo: "&amp;IF(D16="","sem prazo",TEXT(D16,"dd/mm"))&amp;IF(F16="Sem prazo","","; "&amp;LOWER(F16))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="17">
@@ -2178,7 +2203,7 @@
       </c>
       <c r="H17" s="28" t="str">
         <f>H16&amp;IF(B17="","",B17&amp;" (dono: "&amp;C17&amp;"; prazo: "&amp;IF(D17="","sem prazo",TEXT(D17,"dd/mm"))&amp;IF(F17="Sem prazo","","; "&amp;LOWER(F17))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="18">
@@ -2207,7 +2232,7 @@
       </c>
       <c r="H18" s="28" t="str">
         <f>H17&amp;IF(B18="","",B18&amp;" (dono: "&amp;C18&amp;"; prazo: "&amp;IF(D18="","sem prazo",TEXT(D18,"dd/mm"))&amp;IF(F18="Sem prazo","","; "&amp;LOWER(F18))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="19">
@@ -2236,7 +2261,7 @@
       </c>
       <c r="H19" s="28" t="str">
         <f>H18&amp;IF(B19="","",B19&amp;" (dono: "&amp;C19&amp;"; prazo: "&amp;IF(D19="","sem prazo",TEXT(D19,"dd/mm"))&amp;IF(F19="Sem prazo","","; "&amp;LOWER(F19))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="20">
@@ -2265,7 +2290,7 @@
       </c>
       <c r="H20" s="28" t="str">
         <f>H19&amp;IF(B20="","",B20&amp;" (dono: "&amp;C20&amp;"; prazo: "&amp;IF(D20="","sem prazo",TEXT(D20,"dd/mm"))&amp;IF(F20="Sem prazo","","; "&amp;LOWER(F20))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="21">
@@ -2294,7 +2319,7 @@
       </c>
       <c r="H21" s="28" t="str">
         <f>H20&amp;IF(B21="","",B21&amp;" (dono: "&amp;C21&amp;"; prazo: "&amp;IF(D21="","sem prazo",TEXT(D21,"dd/mm"))&amp;IF(F21="Sem prazo","","; "&amp;LOWER(F21))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="22">
@@ -2323,7 +2348,7 @@
       </c>
       <c r="H22" s="28" t="str">
         <f>H21&amp;IF(B22="","",B22&amp;" (dono: "&amp;C22&amp;"; prazo: "&amp;IF(D22="","sem prazo",TEXT(D22,"dd/mm"))&amp;IF(F22="Sem prazo","","; "&amp;LOWER(F22))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="23">
@@ -2352,7 +2377,7 @@
       </c>
       <c r="H23" s="28" t="str">
         <f>H22&amp;IF(B23="","",B23&amp;" (dono: "&amp;C23&amp;"; prazo: "&amp;IF(D23="","sem prazo",TEXT(D23,"dd/mm"))&amp;IF(F23="Sem prazo","","; "&amp;LOWER(F23))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="24">
@@ -2381,7 +2406,7 @@
       </c>
       <c r="H24" s="28" t="str">
         <f>H23&amp;IF(B24="","",B24&amp;" (dono: "&amp;C24&amp;"; prazo: "&amp;IF(D24="","sem prazo",TEXT(D24,"dd/mm"))&amp;IF(F24="Sem prazo","","; "&amp;LOWER(F24))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="25">
@@ -2410,7 +2435,7 @@
       </c>
       <c r="H25" s="28" t="str">
         <f>H24&amp;IF(B25="","",B25&amp;" (dono: "&amp;C25&amp;"; prazo: "&amp;IF(D25="","sem prazo",TEXT(D25,"dd/mm"))&amp;IF(F25="Sem prazo","","; "&amp;LOWER(F25))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="26">
@@ -2439,7 +2464,7 @@
       </c>
       <c r="H26" s="28" t="str">
         <f>H25&amp;IF(B26="","",B26&amp;" (dono: "&amp;C26&amp;"; prazo: "&amp;IF(D26="","sem prazo",TEXT(D26,"dd/mm"))&amp;IF(F26="Sem prazo","","; "&amp;LOWER(F26))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="27">
@@ -2468,7 +2493,7 @@
       </c>
       <c r="H27" s="28" t="str">
         <f>H26&amp;IF(B27="","",B27&amp;" (dono: "&amp;C27&amp;"; prazo: "&amp;IF(D27="","sem prazo",TEXT(D27,"dd/mm"))&amp;IF(F27="Sem prazo","","; "&amp;LOWER(F27))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="28">
@@ -2497,7 +2522,7 @@
       </c>
       <c r="H28" s="28" t="str">
         <f>H27&amp;IF(B28="","",B28&amp;" (dono: "&amp;C28&amp;"; prazo: "&amp;IF(D28="","sem prazo",TEXT(D28,"dd/mm"))&amp;IF(F28="Sem prazo","","; "&amp;LOWER(F28))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="29">
@@ -2526,7 +2551,7 @@
       </c>
       <c r="H29" s="28" t="str">
         <f>H28&amp;IF(B29="","",B29&amp;" (dono: "&amp;C29&amp;"; prazo: "&amp;IF(D29="","sem prazo",TEXT(D29,"dd/mm"))&amp;IF(F29="Sem prazo","","; "&amp;LOWER(F29))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="30">
@@ -2555,7 +2580,7 @@
       </c>
       <c r="H30" s="28" t="str">
         <f>H29&amp;IF(B30="","",B30&amp;" (dono: "&amp;C30&amp;"; prazo: "&amp;IF(D30="","sem prazo",TEXT(D30,"dd/mm"))&amp;IF(F30="Sem prazo","","; "&amp;LOWER(F30))&amp;") | ")</f>
-        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
+        <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
     <row r="32">
@@ -2571,7 +2596,7 @@
         <v>Reunião: Semanal da equipe · 10/09/2026
 Participantes: Ana; Bruno; Carla; Diego
 Decisões: Manual da Padaria atrasou: Carla fecha até 15/09; Diego prepara o servidor do site; reunião com o Bistrô na quarta
-Pendências: Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; atrasada) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo)</v>
+Pendências: Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo)</v>
       </c>
     </row>
     <row r="34"/>
@@ -2642,9 +2667,13 @@
           <t>Data de referência (hoje)</t>
         </is>
       </c>
-      <c r="B5" s="32">
-        <f>TODAY()</f>
-        <v>46282.0</v>
+      <c r="B5" s="32" t="n">
+        <v>46279</v>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para os arquivos do kit mostrarem a mesma foto. Ao usar com os seus dados, troque por =HOJE().</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -2903,7 +2932,7 @@
       </c>
       <c r="G7" s="21">
         <f>IF(C7="","",COUNTIFS(Pendências!$A$5:$A$304,A7,Pendências!$H$5:$H$304,"Atrasada"))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2935,7 +2964,7 @@
       </c>
       <c r="G8" s="21">
         <f>IF(C8="","",COUNTIFS(Pendências!$A$5:$A$304,A8,Pendências!$H$5:$H$304,"Atrasada"))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -4908,11 +4937,11 @@
       </c>
       <c r="I7" s="24">
         <f>IF(OR(B7="",F7="Feito",D7=""),"",D7-Config!$B$5)</f>
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="J7" s="28">
         <f>IF(OR(B7="",F7="Feito"),0,IF(H7="Atrasada",3000+MIN(Config!$B$5-D7,60),IF(H7="Hoje",2500,IF(H7="Esta semana",2000-(D7-Config!$B$5),IF(H7="Sem prazo",500,1000-MIN(D7-Config!$B$5,900)))))+IF(E7="Alta",200,IF(E7="Média",100,0))-ROW()/100000)</f>
-        <v>3204.99993</v>
+        <v>3201.99993</v>
       </c>
       <c r="K7" s="28">
         <f>IF(AND(B7&lt;&gt;"",A7=Config!$B$6),COUNTIFS($A$5:A7,Config!$B$6,$B$5:B7,"&lt;&gt;"),"")</f>
@@ -5098,15 +5127,15 @@
       <c r="G11" s="34" t="n"/>
       <c r="H11" s="21" t="str">
         <f>IF(B11="","",IF(F11="Feito","Feita",IF(D11="","Sem prazo",IF(D11&lt;Config!$B$5,"Atrasada",IF(D11=Config!$B$5,"Hoje",IF(D11-Config!$B$5&lt;=7,"Esta semana","No prazo"))))))</f>
-        <v>Atrasada</v>
+        <v>Esta semana</v>
       </c>
       <c r="I11" s="24">
         <f>IF(OR(B11="",F11="Feito",D11=""),"",D11-Config!$B$5)</f>
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="28">
         <f>IF(OR(B11="",F11="Feito"),0,IF(H11="Atrasada",3000+MIN(Config!$B$5-D11,60),IF(H11="Hoje",2500,IF(H11="Esta semana",2000-(D11-Config!$B$5),IF(H11="Sem prazo",500,1000-MIN(D11-Config!$B$5,900)))))+IF(E11="Alta",200,IF(E11="Média",100,0))-ROW()/100000)</f>
-        <v>3100.99989</v>
+        <v>2097.99989</v>
       </c>
       <c r="K11" s="28">
         <f>IF(AND(B11&lt;&gt;"",A11=Config!$B$6),COUNTIFS($A$5:A11,Config!$B$6,$B$5:B11,"&lt;&gt;"),"")</f>
@@ -5145,15 +5174,15 @@
       <c r="G12" s="34" t="n"/>
       <c r="H12" s="21" t="str">
         <f>IF(B12="","",IF(F12="Feito","Feita",IF(D12="","Sem prazo",IF(D12&lt;Config!$B$5,"Atrasada",IF(D12=Config!$B$5,"Hoje",IF(D12-Config!$B$5&lt;=7,"Esta semana","No prazo"))))))</f>
-        <v>Atrasada</v>
+        <v>Esta semana</v>
       </c>
       <c r="I12" s="24">
         <f>IF(OR(B12="",F12="Feito",D12=""),"",D12-Config!$B$5)</f>
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="J12" s="28">
         <f>IF(OR(B12="",F12="Feito"),0,IF(H12="Atrasada",3000+MIN(Config!$B$5-D12,60),IF(H12="Hoje",2500,IF(H12="Esta semana",2000-(D12-Config!$B$5),IF(H12="Sem prazo",500,1000-MIN(D12-Config!$B$5,900)))))+IF(E12="Alta",200,IF(E12="Média",100,0))-ROW()/100000)</f>
-        <v>3201.99988</v>
+        <v>2198.99988</v>
       </c>
       <c r="K12" s="28">
         <f>IF(AND(B12&lt;&gt;"",A12=Config!$B$6),COUNTIFS($A$5:A12,Config!$B$6,$B$5:B12,"&lt;&gt;"),"")</f>
@@ -5196,11 +5225,11 @@
       </c>
       <c r="I13" s="24">
         <f>IF(OR(B13="",F13="Feito",D13=""),"",D13-Config!$B$5)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J13" s="28">
         <f>IF(OR(B13="",F13="Feito"),0,IF(H13="Atrasada",3000+MIN(Config!$B$5-D13,60),IF(H13="Hoje",2500,IF(H13="Esta semana",2000-(D13-Config!$B$5),IF(H13="Sem prazo",500,1000-MIN(D13-Config!$B$5,900)))))+IF(E13="Alta",200,IF(E13="Média",100,0))-ROW()/100000)</f>
-        <v>2098.99987</v>
+        <v>2095.99987</v>
       </c>
       <c r="K13" s="28">
         <f>IF(AND(B13&lt;&gt;"",A13=Config!$B$6),COUNTIFS($A$5:A13,Config!$B$6,$B$5:B13,"&lt;&gt;"),"")</f>
@@ -5243,11 +5272,11 @@
       </c>
       <c r="I14" s="24">
         <f>IF(OR(B14="",F14="Feito",D14=""),"",D14-Config!$B$5)</f>
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="J14" s="28">
         <f>IF(OR(B14="",F14="Feito"),0,IF(H14="Atrasada",3000+MIN(Config!$B$5-D14,60),IF(H14="Hoje",2500,IF(H14="Esta semana",2000-(D14-Config!$B$5),IF(H14="Sem prazo",500,1000-MIN(D14-Config!$B$5,900)))))+IF(E14="Alta",200,IF(E14="Média",100,0))-ROW()/100000)</f>
-        <v>3105.99986</v>
+        <v>3102.99986</v>
       </c>
       <c r="K14" s="28">
         <f>IF(AND(B14&lt;&gt;"",A14=Config!$B$6),COUNTIFS($A$5:A14,Config!$B$6,$B$5:B14,"&lt;&gt;"),"")</f>
@@ -5290,11 +5319,11 @@
       </c>
       <c r="I15" s="24">
         <f>IF(OR(B15="",F15="Feito",D15=""),"",D15-Config!$B$5)</f>
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="J15" s="28">
         <f>IF(OR(B15="",F15="Feito"),0,IF(H15="Atrasada",3000+MIN(Config!$B$5-D15,60),IF(H15="Hoje",2500,IF(H15="Esta semana",2000-(D15-Config!$B$5),IF(H15="Sem prazo",500,1000-MIN(D15-Config!$B$5,900)))))+IF(E15="Alta",200,IF(E15="Média",100,0))-ROW()/100000)</f>
-        <v>3003.99985</v>
+        <v>3000.99985</v>
       </c>
       <c r="K15" s="28">
         <f>IF(AND(B15&lt;&gt;"",A15=Config!$B$6),COUNTIFS($A$5:A15,Config!$B$6,$B$5:B15,"&lt;&gt;"),"")</f>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
@@ -830,7 +830,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
@@ -897,7 +897,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="5" t="str">
-        <f>Config!B4&amp;" · pendências em "&amp;TEXT(Config!B5,"dd/mm/yyyy")</f>
+        <f>Config!B4&amp;" · pendências em "&amp;TEXT(DAY(Config!B5),"00")&amp;"/"&amp;TEXT(MONTH(Config!B5),"00")&amp;"/"&amp;YEAR(Config!B5)</f>
         <v>Prisma Comunicação (exemplo fictício) · pendências em 14/09/2026</v>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
         <v>Esta semana</v>
       </c>
       <c r="H11" s="28" t="str">
-        <f>""&amp;IF(B11="","",B11&amp;" (dono: "&amp;C11&amp;"; prazo: "&amp;IF(D11="","sem prazo",TEXT(D11,"dd/mm"))&amp;IF(F11="Sem prazo","","; "&amp;LOWER(F11))&amp;") | ")</f>
+        <f>""&amp;IF(B11="","",B11&amp;" (dono: "&amp;C11&amp;"; prazo: "&amp;IF(D11="","sem prazo",TEXT(DAY(D11),"00")&amp;"/"&amp;TEXT(MONTH(D11),"00"))&amp;IF(F11="Sem prazo","","; "&amp;LOWER(F11))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | </v>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         <v>Esta semana</v>
       </c>
       <c r="H12" s="28" t="str">
-        <f>H11&amp;IF(B12="","",B12&amp;" (dono: "&amp;C12&amp;"; prazo: "&amp;IF(D12="","sem prazo",TEXT(D12,"dd/mm"))&amp;IF(F12="Sem prazo","","; "&amp;LOWER(F12))&amp;") | ")</f>
+        <f>H11&amp;IF(B12="","",B12&amp;" (dono: "&amp;C12&amp;"; prazo: "&amp;IF(D12="","sem prazo",TEXT(DAY(D12),"00")&amp;"/"&amp;TEXT(MONTH(D12),"00"))&amp;IF(F12="Sem prazo","","; "&amp;LOWER(F12))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | </v>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
         <v>Atrasada</v>
       </c>
       <c r="H13" s="28" t="str">
-        <f>H12&amp;IF(B13="","",B13&amp;" (dono: "&amp;C13&amp;"; prazo: "&amp;IF(D13="","sem prazo",TEXT(D13,"dd/mm"))&amp;IF(F13="Sem prazo","","; "&amp;LOWER(F13))&amp;") | ")</f>
+        <f>H12&amp;IF(B13="","",B13&amp;" (dono: "&amp;C13&amp;"; prazo: "&amp;IF(D13="","sem prazo",TEXT(DAY(D13),"00")&amp;"/"&amp;TEXT(MONTH(D13),"00"))&amp;IF(F13="Sem prazo","","; "&amp;LOWER(F13))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | </v>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         <v>Atrasada</v>
       </c>
       <c r="H14" s="28" t="str">
-        <f>H13&amp;IF(B14="","",B14&amp;" (dono: "&amp;C14&amp;"; prazo: "&amp;IF(D14="","sem prazo",TEXT(D14,"dd/mm"))&amp;IF(F14="Sem prazo","","; "&amp;LOWER(F14))&amp;") | ")</f>
+        <f>H13&amp;IF(B14="","",B14&amp;" (dono: "&amp;C14&amp;"; prazo: "&amp;IF(D14="","sem prazo",TEXT(DAY(D14),"00")&amp;"/"&amp;TEXT(MONTH(D14),"00"))&amp;IF(F14="Sem prazo","","; "&amp;LOWER(F14))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | </v>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
         <v>Sem prazo</v>
       </c>
       <c r="H15" s="28" t="str">
-        <f>H14&amp;IF(B15="","",B15&amp;" (dono: "&amp;C15&amp;"; prazo: "&amp;IF(D15="","sem prazo",TEXT(D15,"dd/mm"))&amp;IF(F15="Sem prazo","","; "&amp;LOWER(F15))&amp;") | ")</f>
+        <f>H14&amp;IF(B15="","",B15&amp;" (dono: "&amp;C15&amp;"; prazo: "&amp;IF(D15="","sem prazo",TEXT(DAY(D15),"00")&amp;"/"&amp;TEXT(MONTH(D15),"00"))&amp;IF(F15="Sem prazo","","; "&amp;LOWER(F15))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2173,7 +2173,7 @@
         <v/>
       </c>
       <c r="H16" s="28" t="str">
-        <f>H15&amp;IF(B16="","",B16&amp;" (dono: "&amp;C16&amp;"; prazo: "&amp;IF(D16="","sem prazo",TEXT(D16,"dd/mm"))&amp;IF(F16="Sem prazo","","; "&amp;LOWER(F16))&amp;") | ")</f>
+        <f>H15&amp;IF(B16="","",B16&amp;" (dono: "&amp;C16&amp;"; prazo: "&amp;IF(D16="","sem prazo",TEXT(DAY(D16),"00")&amp;"/"&amp;TEXT(MONTH(D16),"00"))&amp;IF(F16="Sem prazo","","; "&amp;LOWER(F16))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
         <v/>
       </c>
       <c r="H17" s="28" t="str">
-        <f>H16&amp;IF(B17="","",B17&amp;" (dono: "&amp;C17&amp;"; prazo: "&amp;IF(D17="","sem prazo",TEXT(D17,"dd/mm"))&amp;IF(F17="Sem prazo","","; "&amp;LOWER(F17))&amp;") | ")</f>
+        <f>H16&amp;IF(B17="","",B17&amp;" (dono: "&amp;C17&amp;"; prazo: "&amp;IF(D17="","sem prazo",TEXT(DAY(D17),"00")&amp;"/"&amp;TEXT(MONTH(D17),"00"))&amp;IF(F17="Sem prazo","","; "&amp;LOWER(F17))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
         <v/>
       </c>
       <c r="H18" s="28" t="str">
-        <f>H17&amp;IF(B18="","",B18&amp;" (dono: "&amp;C18&amp;"; prazo: "&amp;IF(D18="","sem prazo",TEXT(D18,"dd/mm"))&amp;IF(F18="Sem prazo","","; "&amp;LOWER(F18))&amp;") | ")</f>
+        <f>H17&amp;IF(B18="","",B18&amp;" (dono: "&amp;C18&amp;"; prazo: "&amp;IF(D18="","sem prazo",TEXT(DAY(D18),"00")&amp;"/"&amp;TEXT(MONTH(D18),"00"))&amp;IF(F18="Sem prazo","","; "&amp;LOWER(F18))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
         <v/>
       </c>
       <c r="H19" s="28" t="str">
-        <f>H18&amp;IF(B19="","",B19&amp;" (dono: "&amp;C19&amp;"; prazo: "&amp;IF(D19="","sem prazo",TEXT(D19,"dd/mm"))&amp;IF(F19="Sem prazo","","; "&amp;LOWER(F19))&amp;") | ")</f>
+        <f>H18&amp;IF(B19="","",B19&amp;" (dono: "&amp;C19&amp;"; prazo: "&amp;IF(D19="","sem prazo",TEXT(DAY(D19),"00")&amp;"/"&amp;TEXT(MONTH(D19),"00"))&amp;IF(F19="Sem prazo","","; "&amp;LOWER(F19))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
         <v/>
       </c>
       <c r="H20" s="28" t="str">
-        <f>H19&amp;IF(B20="","",B20&amp;" (dono: "&amp;C20&amp;"; prazo: "&amp;IF(D20="","sem prazo",TEXT(D20,"dd/mm"))&amp;IF(F20="Sem prazo","","; "&amp;LOWER(F20))&amp;") | ")</f>
+        <f>H19&amp;IF(B20="","",B20&amp;" (dono: "&amp;C20&amp;"; prazo: "&amp;IF(D20="","sem prazo",TEXT(DAY(D20),"00")&amp;"/"&amp;TEXT(MONTH(D20),"00"))&amp;IF(F20="Sem prazo","","; "&amp;LOWER(F20))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v/>
       </c>
       <c r="H21" s="28" t="str">
-        <f>H20&amp;IF(B21="","",B21&amp;" (dono: "&amp;C21&amp;"; prazo: "&amp;IF(D21="","sem prazo",TEXT(D21,"dd/mm"))&amp;IF(F21="Sem prazo","","; "&amp;LOWER(F21))&amp;") | ")</f>
+        <f>H20&amp;IF(B21="","",B21&amp;" (dono: "&amp;C21&amp;"; prazo: "&amp;IF(D21="","sem prazo",TEXT(DAY(D21),"00")&amp;"/"&amp;TEXT(MONTH(D21),"00"))&amp;IF(F21="Sem prazo","","; "&amp;LOWER(F21))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
         <v/>
       </c>
       <c r="H22" s="28" t="str">
-        <f>H21&amp;IF(B22="","",B22&amp;" (dono: "&amp;C22&amp;"; prazo: "&amp;IF(D22="","sem prazo",TEXT(D22,"dd/mm"))&amp;IF(F22="Sem prazo","","; "&amp;LOWER(F22))&amp;") | ")</f>
+        <f>H21&amp;IF(B22="","",B22&amp;" (dono: "&amp;C22&amp;"; prazo: "&amp;IF(D22="","sem prazo",TEXT(DAY(D22),"00")&amp;"/"&amp;TEXT(MONTH(D22),"00"))&amp;IF(F22="Sem prazo","","; "&amp;LOWER(F22))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
         <v/>
       </c>
       <c r="H23" s="28" t="str">
-        <f>H22&amp;IF(B23="","",B23&amp;" (dono: "&amp;C23&amp;"; prazo: "&amp;IF(D23="","sem prazo",TEXT(D23,"dd/mm"))&amp;IF(F23="Sem prazo","","; "&amp;LOWER(F23))&amp;") | ")</f>
+        <f>H22&amp;IF(B23="","",B23&amp;" (dono: "&amp;C23&amp;"; prazo: "&amp;IF(D23="","sem prazo",TEXT(DAY(D23),"00")&amp;"/"&amp;TEXT(MONTH(D23),"00"))&amp;IF(F23="Sem prazo","","; "&amp;LOWER(F23))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
         <v/>
       </c>
       <c r="H24" s="28" t="str">
-        <f>H23&amp;IF(B24="","",B24&amp;" (dono: "&amp;C24&amp;"; prazo: "&amp;IF(D24="","sem prazo",TEXT(D24,"dd/mm"))&amp;IF(F24="Sem prazo","","; "&amp;LOWER(F24))&amp;") | ")</f>
+        <f>H23&amp;IF(B24="","",B24&amp;" (dono: "&amp;C24&amp;"; prazo: "&amp;IF(D24="","sem prazo",TEXT(DAY(D24),"00")&amp;"/"&amp;TEXT(MONTH(D24),"00"))&amp;IF(F24="Sem prazo","","; "&amp;LOWER(F24))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
         <v/>
       </c>
       <c r="H25" s="28" t="str">
-        <f>H24&amp;IF(B25="","",B25&amp;" (dono: "&amp;C25&amp;"; prazo: "&amp;IF(D25="","sem prazo",TEXT(D25,"dd/mm"))&amp;IF(F25="Sem prazo","","; "&amp;LOWER(F25))&amp;") | ")</f>
+        <f>H24&amp;IF(B25="","",B25&amp;" (dono: "&amp;C25&amp;"; prazo: "&amp;IF(D25="","sem prazo",TEXT(DAY(D25),"00")&amp;"/"&amp;TEXT(MONTH(D25),"00"))&amp;IF(F25="Sem prazo","","; "&amp;LOWER(F25))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
         <v/>
       </c>
       <c r="H26" s="28" t="str">
-        <f>H25&amp;IF(B26="","",B26&amp;" (dono: "&amp;C26&amp;"; prazo: "&amp;IF(D26="","sem prazo",TEXT(D26,"dd/mm"))&amp;IF(F26="Sem prazo","","; "&amp;LOWER(F26))&amp;") | ")</f>
+        <f>H25&amp;IF(B26="","",B26&amp;" (dono: "&amp;C26&amp;"; prazo: "&amp;IF(D26="","sem prazo",TEXT(DAY(D26),"00")&amp;"/"&amp;TEXT(MONTH(D26),"00"))&amp;IF(F26="Sem prazo","","; "&amp;LOWER(F26))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
         <v/>
       </c>
       <c r="H27" s="28" t="str">
-        <f>H26&amp;IF(B27="","",B27&amp;" (dono: "&amp;C27&amp;"; prazo: "&amp;IF(D27="","sem prazo",TEXT(D27,"dd/mm"))&amp;IF(F27="Sem prazo","","; "&amp;LOWER(F27))&amp;") | ")</f>
+        <f>H26&amp;IF(B27="","",B27&amp;" (dono: "&amp;C27&amp;"; prazo: "&amp;IF(D27="","sem prazo",TEXT(DAY(D27),"00")&amp;"/"&amp;TEXT(MONTH(D27),"00"))&amp;IF(F27="Sem prazo","","; "&amp;LOWER(F27))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v/>
       </c>
       <c r="H28" s="28" t="str">
-        <f>H27&amp;IF(B28="","",B28&amp;" (dono: "&amp;C28&amp;"; prazo: "&amp;IF(D28="","sem prazo",TEXT(D28,"dd/mm"))&amp;IF(F28="Sem prazo","","; "&amp;LOWER(F28))&amp;") | ")</f>
+        <f>H27&amp;IF(B28="","",B28&amp;" (dono: "&amp;C28&amp;"; prazo: "&amp;IF(D28="","sem prazo",TEXT(DAY(D28),"00")&amp;"/"&amp;TEXT(MONTH(D28),"00"))&amp;IF(F28="Sem prazo","","; "&amp;LOWER(F28))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
         <v/>
       </c>
       <c r="H29" s="28" t="str">
-        <f>H28&amp;IF(B29="","",B29&amp;" (dono: "&amp;C29&amp;"; prazo: "&amp;IF(D29="","sem prazo",TEXT(D29,"dd/mm"))&amp;IF(F29="Sem prazo","","; "&amp;LOWER(F29))&amp;") | ")</f>
+        <f>H28&amp;IF(B29="","",B29&amp;" (dono: "&amp;C29&amp;"; prazo: "&amp;IF(D29="","sem prazo",TEXT(DAY(D29),"00")&amp;"/"&amp;TEXT(MONTH(D29),"00"))&amp;IF(F29="Sem prazo","","; "&amp;LOWER(F29))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
         <v/>
       </c>
       <c r="H30" s="28" t="str">
-        <f>H29&amp;IF(B30="","",B30&amp;" (dono: "&amp;C30&amp;"; prazo: "&amp;IF(D30="","sem prazo",TEXT(D30,"dd/mm"))&amp;IF(F30="Sem prazo","","; "&amp;LOWER(F30))&amp;") | ")</f>
+        <f>H29&amp;IF(B30="","",B30&amp;" (dono: "&amp;C30&amp;"; prazo: "&amp;IF(D30="","sem prazo",TEXT(DAY(D30),"00")&amp;"/"&amp;TEXT(MONTH(D30),"00"))&amp;IF(F30="Sem prazo","","; "&amp;LOWER(F30))&amp;") | ")</f>
         <v>Fechar o manual da marca da Padaria (dono: Carla; prazo: 15/09; esta semana) | Preparar o servidor e o domínio do site (dono: Diego; prazo: 18/09; esta semana) | Confirmar a reunião de quarta com o Bistrô (dono: Ana; prazo: 11/09; atrasada) | Levantar custo do freela de motion (dono: Ana; prazo: 13/09; atrasada) | Revisar a proposta comercial da Aurora (dono: Ana; prazo: sem prazo) | </v>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="33">
       <c r="A33" s="29" t="str">
-        <f>"Reunião: "&amp;B5&amp;" · "&amp;TEXT(B4,"dd/mm/yyyy")&amp;CHAR(10)&amp;"Participantes: "&amp;B6&amp;CHAR(10)&amp;"Decisões: "&amp;B7&amp;CHAR(10)&amp;"Pendências: "&amp;IF(LEN(H30)&gt;3,LEFT(H30,LEN(H30)-3),"nenhuma")</f>
+        <f>"Reunião: "&amp;B5&amp;" · "&amp;TEXT(DAY(B4),"00")&amp;"/"&amp;TEXT(MONTH(B4),"00")&amp;"/"&amp;YEAR(B4)&amp;CHAR(10)&amp;"Participantes: "&amp;B6&amp;CHAR(10)&amp;"Decisões: "&amp;B7&amp;CHAR(10)&amp;"Pendências: "&amp;IF(LEN(H30)&gt;3,LEFT(H30,LEN(H30)-3),"nenhuma")</f>
         <v>Reunião: Semanal da equipe · 10/09/2026
 Participantes: Ana; Bruno; Carla; Diego
 Decisões: Manual da Padaria atrasou: Carla fecha até 15/09; Diego prepara o servidor do site; reunião com o Bistrô na quarta

--- a/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-completo/05-ata-e-pendencias.xlsx
@@ -702,6 +702,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -830,7 +831,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e semáforos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
